--- a/5. Knife/output/yearly_total_coral_cover_growth_param_0.5.xlsx
+++ b/5. Knife/output/yearly_total_coral_cover_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2.23499815502015</v>
+        <v>2.356979998166378</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6665046732057575</v>
+        <v>0.6986645761382972</v>
       </c>
       <c r="D3" t="n">
-        <v>5.643841749742936</v>
+        <v>5.868514711859818</v>
       </c>
       <c r="E3" t="n">
-        <v>8.545344577968844</v>
+        <v>8.924159286164494</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.927129867597078</v>
+        <v>3.192257142255893</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6759136594198439</v>
+        <v>0.7311172436329932</v>
       </c>
       <c r="D4" t="n">
-        <v>5.640493990071454</v>
+        <v>6.137462851759004</v>
       </c>
       <c r="E4" t="n">
-        <v>9.243537517088376</v>
+        <v>10.06083723764789</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.179201802208247</v>
+        <v>4.629158696833278</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6988865556992194</v>
+        <v>0.7902177560774075</v>
       </c>
       <c r="D5" t="n">
-        <v>5.600585945893822</v>
+        <v>6.324777304950213</v>
       </c>
       <c r="E5" t="n">
-        <v>10.47867430380129</v>
+        <v>11.7441537578609</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.877733322802697</v>
+        <v>6.584707935798312</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7309013483347079</v>
+        <v>0.8592901298115707</v>
       </c>
       <c r="D6" t="n">
-        <v>5.674069761556695</v>
+        <v>6.715746911440626</v>
       </c>
       <c r="E6" t="n">
-        <v>12.2827044326941</v>
+        <v>14.15974497705051</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.332190940713105</v>
+        <v>9.414814763310536</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7684041106369359</v>
+        <v>0.9390161174894586</v>
       </c>
       <c r="D7" t="n">
-        <v>5.679763898241326</v>
+        <v>6.96858732325405</v>
       </c>
       <c r="E7" t="n">
-        <v>14.78035894959137</v>
+        <v>17.32241820405405</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.73269009886687</v>
+        <v>13.21949039214331</v>
       </c>
       <c r="C8" t="n">
-        <v>0.810560357057294</v>
+        <v>1.02920256207248</v>
       </c>
       <c r="D8" t="n">
-        <v>5.731875066382747</v>
+        <v>7.304679547819191</v>
       </c>
       <c r="E8" t="n">
-        <v>18.27512552230691</v>
+        <v>21.55337250203498</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.97374200644266</v>
+        <v>17.82125548977338</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8448626218436776</v>
+        <v>1.112169539308864</v>
       </c>
       <c r="D9" t="n">
-        <v>5.84035818770202</v>
+        <v>7.735663648933023</v>
       </c>
       <c r="E9" t="n">
-        <v>22.65896281598836</v>
+        <v>26.66908867801527</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>21.00776135221565</v>
+        <v>23.08896769706465</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8763374532418303</v>
+        <v>1.193555543045595</v>
       </c>
       <c r="D10" t="n">
-        <v>5.878126021884396</v>
+        <v>8.057121627582731</v>
       </c>
       <c r="E10" t="n">
-        <v>27.76222482734187</v>
+        <v>32.33964486769298</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26.51187095121313</v>
+        <v>28.59859263321256</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8994183417686729</v>
+        <v>1.260781875223798</v>
       </c>
       <c r="D11" t="n">
-        <v>5.84572834764425</v>
+        <v>8.230762478507799</v>
       </c>
       <c r="E11" t="n">
-        <v>33.25701764062605</v>
+        <v>38.09013698694416</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>32.06375239349928</v>
+        <v>34.00039636295841</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9100801218367933</v>
+        <v>1.316619202905152</v>
       </c>
       <c r="D12" t="n">
-        <v>5.751382393266132</v>
+        <v>8.314836052081054</v>
       </c>
       <c r="E12" t="n">
-        <v>38.7252149086022</v>
+        <v>43.63185161794462</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>37.17704786639019</v>
+        <v>38.80015798003913</v>
       </c>
       <c r="C13" t="n">
-        <v>0.9185035171392308</v>
+        <v>1.35394282185519</v>
       </c>
       <c r="D13" t="n">
-        <v>5.72114456397533</v>
+        <v>8.516457017617892</v>
       </c>
       <c r="E13" t="n">
-        <v>43.81669594750475</v>
+        <v>48.67055781951221</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>41.52124218777416</v>
+        <v>42.70669282595578</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9173548723252621</v>
+        <v>1.370545844846419</v>
       </c>
       <c r="D14" t="n">
-        <v>5.596855304617684</v>
+        <v>8.518773572235316</v>
       </c>
       <c r="E14" t="n">
-        <v>48.0354523647171</v>
+        <v>52.59601224303752</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>44.95444336195638</v>
+        <v>45.78672636931495</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9030115383662162</v>
+        <v>1.369532831730691</v>
       </c>
       <c r="D15" t="n">
-        <v>5.510893475633833</v>
+        <v>8.626149443133803</v>
       </c>
       <c r="E15" t="n">
-        <v>51.36834837595643</v>
+        <v>55.78240864417944</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>27.60599931516508</v>
+        <v>28.63216128555202</v>
       </c>
       <c r="C16" t="n">
-        <v>0.60942970488825</v>
+        <v>0.9263673162502478</v>
       </c>
       <c r="D16" t="n">
-        <v>4.296422478095316</v>
+        <v>6.901784535625501</v>
       </c>
       <c r="E16" t="n">
-        <v>32.51185149814865</v>
+        <v>36.46031313742777</v>
       </c>
     </row>
   </sheetData>
